--- a/phase-1/TOPSIS.xlsx
+++ b/phase-1/TOPSIS.xlsx
@@ -1,22 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Polina\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ilona\Desktop\ProjectManagment_CSF_2026\phase-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19589A33-F262-487C-B5CE-C71323DDC2C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Справочник" sheetId="1" r:id="rId1"/>
     <sheet name="Ввод" sheetId="2" r:id="rId2"/>
     <sheet name="Расчет" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -212,7 +226,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
@@ -629,31 +643,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -661,7 +675,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -669,7 +683,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -677,7 +691,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>9</v>
       </c>
@@ -688,7 +702,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -699,7 +713,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
@@ -710,7 +724,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>18</v>
       </c>
@@ -721,7 +735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>21</v>
       </c>
@@ -732,7 +746,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>9</v>
       </c>
@@ -743,7 +757,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>26</v>
       </c>
@@ -754,7 +768,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>29</v>
       </c>
@@ -765,7 +779,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>31</v>
       </c>
@@ -776,7 +790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>33</v>
       </c>
@@ -787,7 +801,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>35</v>
       </c>
@@ -804,26 +818,26 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="str">
         <f>"Эксперт 1: "&amp;Справочник!$B$4</f>
         <v>Эксперт 1: Петров Артем</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>38</v>
       </c>
@@ -848,7 +862,7 @@
         <v>Интерес и экспертиза команды</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>39</v>
       </c>
@@ -868,7 +882,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>40</v>
       </c>
@@ -893,7 +907,7 @@
         <v>Интерес и экспертиза команды</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="str">
         <f>Справочник!$B$10</f>
         <v>Бронь</v>
@@ -914,7 +928,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="str">
         <f>Справочник!$B$11</f>
         <v>Бюджет</v>
@@ -935,7 +949,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="str">
         <f>Справочник!$B$12</f>
         <v>Запись</v>
@@ -956,7 +970,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="str">
         <f>Справочник!$B$13</f>
         <v>Привычки</v>
@@ -977,13 +991,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="str">
         <f>"Эксперт 2: "&amp;Справочник!$B$5</f>
         <v>Эксперт 2: Попова Полина</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>38</v>
       </c>
@@ -1008,7 +1022,7 @@
         <v>Интерес и экспертиза команды</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
@@ -1028,7 +1042,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>40</v>
       </c>
@@ -1053,7 +1067,7 @@
         <v>Интерес и экспертиза команды</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="str">
         <f>Справочник!$B$10</f>
         <v>Бронь</v>
@@ -1074,7 +1088,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="str">
         <f>Справочник!$B$11</f>
         <v>Бюджет</v>
@@ -1095,7 +1109,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="str">
         <f>Справочник!$B$12</f>
         <v>Запись</v>
@@ -1116,7 +1130,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="str">
         <f>Справочник!$B$13</f>
         <v>Привычки</v>
@@ -1137,13 +1151,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="str">
         <f>"Эксперт 3: "&amp;Справочник!$B$6</f>
         <v>Эксперт 3: Пауликайте Елона</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>38</v>
       </c>
@@ -1168,17 +1182,27 @@
         <v>Интерес и экспертиза команды</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-    </row>
-    <row r="33" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="6">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>6</v>
+      </c>
+      <c r="D31" s="6">
+        <v>8</v>
+      </c>
+      <c r="E31" s="6">
+        <v>5</v>
+      </c>
+      <c r="F31" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>40</v>
       </c>
@@ -1203,53 +1227,93 @@
         <v>Интерес и экспертиза команды</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="str">
         <f>Справочник!$B$10</f>
         <v>Бронь</v>
       </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B34" s="6">
+        <v>6</v>
+      </c>
+      <c r="C34" s="6">
+        <v>7</v>
+      </c>
+      <c r="D34" s="6">
+        <v>8</v>
+      </c>
+      <c r="E34" s="6">
+        <v>6</v>
+      </c>
+      <c r="F34" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="str">
         <f>Справочник!$B$11</f>
         <v>Бюджет</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B35" s="6">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>5</v>
+      </c>
+      <c r="D35" s="6">
+        <v>7</v>
+      </c>
+      <c r="E35" s="6">
+        <v>5</v>
+      </c>
+      <c r="F35" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="str">
         <f>Справочник!$B$12</f>
         <v>Запись</v>
       </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B36" s="6">
+        <v>8</v>
+      </c>
+      <c r="C36" s="6">
+        <v>6</v>
+      </c>
+      <c r="D36" s="6">
+        <v>9</v>
+      </c>
+      <c r="E36" s="6">
+        <v>6</v>
+      </c>
+      <c r="F36" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="str">
         <f>Справочник!$B$13</f>
         <v>Привычки</v>
       </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
+      <c r="B37" s="6">
+        <v>7</v>
+      </c>
+      <c r="C37" s="6">
+        <v>8</v>
+      </c>
+      <c r="D37" s="6">
+        <v>5</v>
+      </c>
+      <c r="E37" s="6">
+        <v>5</v>
+      </c>
+      <c r="F37" s="6">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="whole" showErrorMessage="1" error="Целое число от 1 до 9" sqref="B5 B8 B9 B10 B11 B18 B21 B22 B23 B24 B31 B34 B35 B36 B37 C5 C8 C9 C10 C11 C18 C21 C22 C23 C24 C31 C34 C35 C36 C37 D5 D8 D9 D10 D11 D18 D21 D22 D23 D24 D31 D34 D35 D36 D37 E5 E8 E9 E10 E11 E18 E21 E22 E23 E24 E31 E34 E35 E36 E37 F5 F8 F9 F10 F11 F18 F21 F22 F23 F24 F31 F34 F35 F36 F37">
+    <dataValidation type="whole" showErrorMessage="1" error="Целое число от 1 до 9" sqref="B8:F11 B21:F24 B31:F31 B5:F5 B18:F18 B34:F37" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>1</formula1>
       <formula2>9</formula2>
     </dataValidation>
@@ -1259,30 +1323,30 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P46"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="16" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>24</v>
       </c>
@@ -1305,162 +1369,162 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="str">
         <f>Справочник!$B$17</f>
         <v>Востребованность</v>
       </c>
-      <c r="B6" s="3" t="str">
+      <c r="B6" s="3">
         <f>IF(COUNT(Ввод!B5,Ввод!B18,Ввод!B31)&lt;3,"",MIN(Ввод!B5,Ввод!B18,Ввод!B31))</f>
-        <v/>
-      </c>
-      <c r="C6" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3">
         <f>IF(COUNT(Ввод!B5,Ввод!B18,Ввод!B31)&lt;3,"",MEDIAN(Ввод!B5,Ввод!B18,Ввод!B31))</f>
-        <v/>
-      </c>
-      <c r="D6" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="D6" s="3">
         <f>IF(COUNT(Ввод!B5,Ввод!B18,Ввод!B31)&lt;3,"",MAX(Ввод!B5,Ввод!B18,Ввод!B31))</f>
-        <v/>
-      </c>
-      <c r="E6" s="7" t="str">
+        <v>7</v>
+      </c>
+      <c r="E6" s="7">
         <f t="shared" ref="E6:G10" si="0">IFERROR(B6/9,"")</f>
-        <v/>
-      </c>
-      <c r="F6" s="7" t="str">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F6" s="7">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G6" s="7" t="str">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G6" s="7">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.77777777777777779</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="str">
         <f>Справочник!$B$18</f>
         <v>Простота реализации MVP</v>
       </c>
-      <c r="B7" s="3" t="str">
+      <c r="B7" s="3">
         <f>IF(COUNT(Ввод!C5,Ввод!C18,Ввод!C31)&lt;3,"",MIN(Ввод!C5,Ввод!C18,Ввод!C31))</f>
-        <v/>
-      </c>
-      <c r="C7" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3">
         <f>IF(COUNT(Ввод!C5,Ввод!C18,Ввод!C31)&lt;3,"",MEDIAN(Ввод!C5,Ввод!C18,Ввод!C31))</f>
-        <v/>
-      </c>
-      <c r="D7" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3">
         <f>IF(COUNT(Ввод!C5,Ввод!C18,Ввод!C31)&lt;3,"",MAX(Ввод!C5,Ввод!C18,Ввод!C31))</f>
-        <v/>
-      </c>
-      <c r="E7" s="7" t="str">
+        <v>7</v>
+      </c>
+      <c r="E7" s="7">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F7" s="7" t="str">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F7" s="7">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G7" s="7" t="str">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G7" s="7">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.77777777777777779</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="str">
         <f>Справочник!$B$19</f>
         <v>Пригодность для оценки и планирования</v>
       </c>
-      <c r="B8" s="3" t="str">
+      <c r="B8" s="3">
         <f>IF(COUNT(Ввод!D5,Ввод!D18,Ввод!D31)&lt;3,"",MIN(Ввод!D5,Ввод!D18,Ввод!D31))</f>
-        <v/>
-      </c>
-      <c r="C8" s="3" t="str">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3">
         <f>IF(COUNT(Ввод!D5,Ввод!D18,Ввод!D31)&lt;3,"",MEDIAN(Ввод!D5,Ввод!D18,Ввод!D31))</f>
-        <v/>
-      </c>
-      <c r="D8" s="3" t="str">
+        <v>8</v>
+      </c>
+      <c r="D8" s="3">
         <f>IF(COUNT(Ввод!D5,Ввод!D18,Ввод!D31)&lt;3,"",MAX(Ввод!D5,Ввод!D18,Ввод!D31))</f>
-        <v/>
-      </c>
-      <c r="E8" s="7" t="str">
+        <v>9</v>
+      </c>
+      <c r="E8" s="7">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F8" s="7" t="str">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="F8" s="7">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G8" s="7" t="str">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="G8" s="7">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="str">
         <f>Справочник!$B$20</f>
         <v>Потенциал монетизации</v>
       </c>
-      <c r="B9" s="3" t="str">
+      <c r="B9" s="3">
         <f>IF(COUNT(Ввод!E5,Ввод!E18,Ввод!E31)&lt;3,"",MIN(Ввод!E5,Ввод!E18,Ввод!E31))</f>
-        <v/>
-      </c>
-      <c r="C9" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="C9" s="3">
         <f>IF(COUNT(Ввод!E5,Ввод!E18,Ввод!E31)&lt;3,"",MEDIAN(Ввод!E5,Ввод!E18,Ввод!E31))</f>
-        <v/>
-      </c>
-      <c r="D9" s="3" t="str">
+        <v>5</v>
+      </c>
+      <c r="D9" s="3">
         <f>IF(COUNT(Ввод!E5,Ввод!E18,Ввод!E31)&lt;3,"",MAX(Ввод!E5,Ввод!E18,Ввод!E31))</f>
-        <v/>
-      </c>
-      <c r="E9" s="7" t="str">
+        <v>5</v>
+      </c>
+      <c r="E9" s="7">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F9" s="7" t="str">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="F9" s="7">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G9" s="7" t="str">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="G9" s="7">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.55555555555555558</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="str">
         <f>Справочник!$B$21</f>
         <v>Интерес и экспертиза команды</v>
       </c>
-      <c r="B10" s="3" t="str">
+      <c r="B10" s="3">
         <f>IF(COUNT(Ввод!F5,Ввод!F18,Ввод!F31)&lt;3,"",MIN(Ввод!F5,Ввод!F18,Ввод!F31))</f>
-        <v/>
-      </c>
-      <c r="C10" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="C10" s="3">
         <f>IF(COUNT(Ввод!F5,Ввод!F18,Ввод!F31)&lt;3,"",MEDIAN(Ввод!F5,Ввод!F18,Ввод!F31))</f>
-        <v/>
-      </c>
-      <c r="D10" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="D10" s="3">
         <f>IF(COUNT(Ввод!F5,Ввод!F18,Ввод!F31)&lt;3,"",MAX(Ввод!F5,Ввод!F18,Ввод!F31))</f>
-        <v/>
-      </c>
-      <c r="E10" s="7" t="str">
+        <v>7</v>
+      </c>
+      <c r="E10" s="7">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F10" s="7" t="str">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F10" s="7">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G10" s="7" t="str">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G10" s="7">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.77777777777777779</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>51</v>
       </c>
@@ -1495,7 +1559,7 @@
       <c r="O13" s="13"/>
       <c r="P13" s="14"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
         <v>44</v>
@@ -1543,276 +1607,276 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="str">
         <f>Справочник!$B$10</f>
         <v>Бронь</v>
       </c>
-      <c r="B15" s="3" t="str">
+      <c r="B15" s="3">
         <f>IF(COUNT(Ввод!B8,Ввод!B21,Ввод!B34)&lt;3,"",MIN(Ввод!B8,Ввод!B21,Ввод!B34))</f>
-        <v/>
-      </c>
-      <c r="C15" s="3" t="str">
+        <v>5</v>
+      </c>
+      <c r="C15" s="3">
         <f>IF(COUNT(Ввод!B8,Ввод!B21,Ввод!B34)&lt;3,"",MEDIAN(Ввод!B8,Ввод!B21,Ввод!B34))</f>
-        <v/>
-      </c>
-      <c r="D15" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="D15" s="3">
         <f>IF(COUNT(Ввод!B8,Ввод!B21,Ввод!B34)&lt;3,"",MAX(Ввод!B8,Ввод!B21,Ввод!B34))</f>
-        <v/>
-      </c>
-      <c r="E15" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="E15" s="3">
         <f>IF(COUNT(Ввод!C8,Ввод!C21,Ввод!C34)&lt;3,"",MIN(Ввод!C8,Ввод!C21,Ввод!C34))</f>
-        <v/>
-      </c>
-      <c r="F15" s="3" t="str">
+        <v>7</v>
+      </c>
+      <c r="F15" s="3">
         <f>IF(COUNT(Ввод!C8,Ввод!C21,Ввод!C34)&lt;3,"",MEDIAN(Ввод!C8,Ввод!C21,Ввод!C34))</f>
-        <v/>
-      </c>
-      <c r="G15" s="3" t="str">
+        <v>7</v>
+      </c>
+      <c r="G15" s="3">
         <f>IF(COUNT(Ввод!C8,Ввод!C21,Ввод!C34)&lt;3,"",MAX(Ввод!C8,Ввод!C21,Ввод!C34))</f>
-        <v/>
-      </c>
-      <c r="H15" s="3" t="str">
+        <v>8</v>
+      </c>
+      <c r="H15" s="3">
         <f>IF(COUNT(Ввод!D8,Ввод!D21,Ввод!D34)&lt;3,"",MIN(Ввод!D8,Ввод!D21,Ввод!D34))</f>
-        <v/>
-      </c>
-      <c r="I15" s="3" t="str">
+        <v>8</v>
+      </c>
+      <c r="I15" s="3">
         <f>IF(COUNT(Ввод!D8,Ввод!D21,Ввод!D34)&lt;3,"",MEDIAN(Ввод!D8,Ввод!D21,Ввод!D34))</f>
-        <v/>
-      </c>
-      <c r="J15" s="3" t="str">
+        <v>8</v>
+      </c>
+      <c r="J15" s="3">
         <f>IF(COUNT(Ввод!D8,Ввод!D21,Ввод!D34)&lt;3,"",MAX(Ввод!D8,Ввод!D21,Ввод!D34))</f>
-        <v/>
-      </c>
-      <c r="K15" s="3" t="str">
+        <v>8</v>
+      </c>
+      <c r="K15" s="3">
         <f>IF(COUNT(Ввод!E8,Ввод!E21,Ввод!E34)&lt;3,"",MIN(Ввод!E8,Ввод!E21,Ввод!E34))</f>
-        <v/>
-      </c>
-      <c r="L15" s="3" t="str">
+        <v>5</v>
+      </c>
+      <c r="L15" s="3">
         <f>IF(COUNT(Ввод!E8,Ввод!E21,Ввод!E34)&lt;3,"",MEDIAN(Ввод!E8,Ввод!E21,Ввод!E34))</f>
-        <v/>
-      </c>
-      <c r="M15" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="M15" s="3">
         <f>IF(COUNT(Ввод!E8,Ввод!E21,Ввод!E34)&lt;3,"",MAX(Ввод!E8,Ввод!E21,Ввод!E34))</f>
-        <v/>
-      </c>
-      <c r="N15" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="N15" s="3">
         <f>IF(COUNT(Ввод!F8,Ввод!F21,Ввод!F34)&lt;3,"",MIN(Ввод!F8,Ввод!F21,Ввод!F34))</f>
-        <v/>
-      </c>
-      <c r="O15" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="O15" s="3">
         <f>IF(COUNT(Ввод!F8,Ввод!F21,Ввод!F34)&lt;3,"",MEDIAN(Ввод!F8,Ввод!F21,Ввод!F34))</f>
-        <v/>
-      </c>
-      <c r="P15" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="P15" s="3">
         <f>IF(COUNT(Ввод!F8,Ввод!F21,Ввод!F34)&lt;3,"",MAX(Ввод!F8,Ввод!F21,Ввод!F34))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="str">
         <f>Справочник!$B$11</f>
         <v>Бюджет</v>
       </c>
-      <c r="B16" s="3" t="str">
+      <c r="B16" s="3">
         <f>IF(COUNT(Ввод!B9,Ввод!B22,Ввод!B35)&lt;3,"",MIN(Ввод!B9,Ввод!B22,Ввод!B35))</f>
-        <v/>
-      </c>
-      <c r="C16" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="C16" s="3">
         <f>IF(COUNT(Ввод!B9,Ввод!B22,Ввод!B35)&lt;3,"",MEDIAN(Ввод!B9,Ввод!B22,Ввод!B35))</f>
-        <v/>
-      </c>
-      <c r="D16" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="D16" s="3">
         <f>IF(COUNT(Ввод!B9,Ввод!B22,Ввод!B35)&lt;3,"",MAX(Ввод!B9,Ввод!B22,Ввод!B35))</f>
-        <v/>
-      </c>
-      <c r="E16" s="3" t="str">
+        <v>7</v>
+      </c>
+      <c r="E16" s="3">
         <f>IF(COUNT(Ввод!C9,Ввод!C22,Ввод!C35)&lt;3,"",MIN(Ввод!C9,Ввод!C22,Ввод!C35))</f>
-        <v/>
-      </c>
-      <c r="F16" s="3" t="str">
+        <v>5</v>
+      </c>
+      <c r="F16" s="3">
         <f>IF(COUNT(Ввод!C9,Ввод!C22,Ввод!C35)&lt;3,"",MEDIAN(Ввод!C9,Ввод!C22,Ввод!C35))</f>
-        <v/>
-      </c>
-      <c r="G16" s="3" t="str">
+        <v>5</v>
+      </c>
+      <c r="G16" s="3">
         <f>IF(COUNT(Ввод!C9,Ввод!C22,Ввод!C35)&lt;3,"",MAX(Ввод!C9,Ввод!C22,Ввод!C35))</f>
-        <v/>
-      </c>
-      <c r="H16" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="H16" s="3">
         <f>IF(COUNT(Ввод!D9,Ввод!D22,Ввод!D35)&lt;3,"",MIN(Ввод!D9,Ввод!D22,Ввод!D35))</f>
-        <v/>
-      </c>
-      <c r="I16" s="3" t="str">
+        <v>5</v>
+      </c>
+      <c r="I16" s="3">
         <f>IF(COUNT(Ввод!D9,Ввод!D22,Ввод!D35)&lt;3,"",MEDIAN(Ввод!D9,Ввод!D22,Ввод!D35))</f>
-        <v/>
-      </c>
-      <c r="J16" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="J16" s="3">
         <f>IF(COUNT(Ввод!D9,Ввод!D22,Ввод!D35)&lt;3,"",MAX(Ввод!D9,Ввод!D22,Ввод!D35))</f>
-        <v/>
-      </c>
-      <c r="K16" s="3" t="str">
+        <v>7</v>
+      </c>
+      <c r="K16" s="3">
         <f>IF(COUNT(Ввод!E9,Ввод!E22,Ввод!E35)&lt;3,"",MIN(Ввод!E9,Ввод!E22,Ввод!E35))</f>
-        <v/>
-      </c>
-      <c r="L16" s="3" t="str">
+        <v>5</v>
+      </c>
+      <c r="L16" s="3">
         <f>IF(COUNT(Ввод!E9,Ввод!E22,Ввод!E35)&lt;3,"",MEDIAN(Ввод!E9,Ввод!E22,Ввод!E35))</f>
-        <v/>
-      </c>
-      <c r="M16" s="3" t="str">
+        <v>5</v>
+      </c>
+      <c r="M16" s="3">
         <f>IF(COUNT(Ввод!E9,Ввод!E22,Ввод!E35)&lt;3,"",MAX(Ввод!E9,Ввод!E22,Ввод!E35))</f>
-        <v/>
-      </c>
-      <c r="N16" s="3" t="str">
+        <v>5</v>
+      </c>
+      <c r="N16" s="3">
         <f>IF(COUNT(Ввод!F9,Ввод!F22,Ввод!F35)&lt;3,"",MIN(Ввод!F9,Ввод!F22,Ввод!F35))</f>
-        <v/>
-      </c>
-      <c r="O16" s="3" t="str">
+        <v>7</v>
+      </c>
+      <c r="O16" s="3">
         <f>IF(COUNT(Ввод!F9,Ввод!F22,Ввод!F35)&lt;3,"",MEDIAN(Ввод!F9,Ввод!F22,Ввод!F35))</f>
-        <v/>
-      </c>
-      <c r="P16" s="3" t="str">
+        <v>7</v>
+      </c>
+      <c r="P16" s="3">
         <f>IF(COUNT(Ввод!F9,Ввод!F22,Ввод!F35)&lt;3,"",MAX(Ввод!F9,Ввод!F22,Ввод!F35))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="str">
         <f>Справочник!$B$12</f>
         <v>Запись</v>
       </c>
-      <c r="B17" s="3" t="str">
+      <c r="B17" s="3">
         <f>IF(COUNT(Ввод!B10,Ввод!B23,Ввод!B36)&lt;3,"",MIN(Ввод!B10,Ввод!B23,Ввод!B36))</f>
-        <v/>
-      </c>
-      <c r="C17" s="3" t="str">
+        <v>8</v>
+      </c>
+      <c r="C17" s="3">
         <f>IF(COUNT(Ввод!B10,Ввод!B23,Ввод!B36)&lt;3,"",MEDIAN(Ввод!B10,Ввод!B23,Ввод!B36))</f>
-        <v/>
-      </c>
-      <c r="D17" s="3" t="str">
+        <v>8</v>
+      </c>
+      <c r="D17" s="3">
         <f>IF(COUNT(Ввод!B10,Ввод!B23,Ввод!B36)&lt;3,"",MAX(Ввод!B10,Ввод!B23,Ввод!B36))</f>
-        <v/>
-      </c>
-      <c r="E17" s="3" t="str">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3">
         <f>IF(COUNT(Ввод!C10,Ввод!C23,Ввод!C36)&lt;3,"",MIN(Ввод!C10,Ввод!C23,Ввод!C36))</f>
-        <v/>
-      </c>
-      <c r="F17" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="F17" s="3">
         <f>IF(COUNT(Ввод!C10,Ввод!C23,Ввод!C36)&lt;3,"",MEDIAN(Ввод!C10,Ввод!C23,Ввод!C36))</f>
-        <v/>
-      </c>
-      <c r="G17" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="G17" s="3">
         <f>IF(COUNT(Ввод!C10,Ввод!C23,Ввод!C36)&lt;3,"",MAX(Ввод!C10,Ввод!C23,Ввод!C36))</f>
-        <v/>
-      </c>
-      <c r="H17" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="H17" s="3">
         <f>IF(COUNT(Ввод!D10,Ввод!D23,Ввод!D36)&lt;3,"",MIN(Ввод!D10,Ввод!D23,Ввод!D36))</f>
-        <v/>
-      </c>
-      <c r="I17" s="3" t="str">
+        <v>9</v>
+      </c>
+      <c r="I17" s="3">
         <f>IF(COUNT(Ввод!D10,Ввод!D23,Ввод!D36)&lt;3,"",MEDIAN(Ввод!D10,Ввод!D23,Ввод!D36))</f>
-        <v/>
-      </c>
-      <c r="J17" s="3" t="str">
+        <v>9</v>
+      </c>
+      <c r="J17" s="3">
         <f>IF(COUNT(Ввод!D10,Ввод!D23,Ввод!D36)&lt;3,"",MAX(Ввод!D10,Ввод!D23,Ввод!D36))</f>
-        <v/>
-      </c>
-      <c r="K17" s="3" t="str">
+        <v>9</v>
+      </c>
+      <c r="K17" s="3">
         <f>IF(COUNT(Ввод!E10,Ввод!E23,Ввод!E36)&lt;3,"",MIN(Ввод!E10,Ввод!E23,Ввод!E36))</f>
-        <v/>
-      </c>
-      <c r="L17" s="3" t="str">
+        <v>5</v>
+      </c>
+      <c r="L17" s="3">
         <f>IF(COUNT(Ввод!E10,Ввод!E23,Ввод!E36)&lt;3,"",MEDIAN(Ввод!E10,Ввод!E23,Ввод!E36))</f>
-        <v/>
-      </c>
-      <c r="M17" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="M17" s="3">
         <f>IF(COUNT(Ввод!E10,Ввод!E23,Ввод!E36)&lt;3,"",MAX(Ввод!E10,Ввод!E23,Ввод!E36))</f>
-        <v/>
-      </c>
-      <c r="N17" s="3" t="str">
+        <v>8</v>
+      </c>
+      <c r="N17" s="3">
         <f>IF(COUNT(Ввод!F10,Ввод!F23,Ввод!F36)&lt;3,"",MIN(Ввод!F10,Ввод!F23,Ввод!F36))</f>
-        <v/>
-      </c>
-      <c r="O17" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="O17" s="3">
         <f>IF(COUNT(Ввод!F10,Ввод!F23,Ввод!F36)&lt;3,"",MEDIAN(Ввод!F10,Ввод!F23,Ввод!F36))</f>
-        <v/>
-      </c>
-      <c r="P17" s="3" t="str">
+        <v>7</v>
+      </c>
+      <c r="P17" s="3">
         <f>IF(COUNT(Ввод!F10,Ввод!F23,Ввод!F36)&lt;3,"",MAX(Ввод!F10,Ввод!F23,Ввод!F36))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="str">
         <f>Справочник!$B$13</f>
         <v>Привычки</v>
       </c>
-      <c r="B18" s="3" t="str">
+      <c r="B18" s="3">
         <f>IF(COUNT(Ввод!B11,Ввод!B24,Ввод!B37)&lt;3,"",MIN(Ввод!B11,Ввод!B24,Ввод!B37))</f>
-        <v/>
-      </c>
-      <c r="C18" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="C18" s="3">
         <f>IF(COUNT(Ввод!B11,Ввод!B24,Ввод!B37)&lt;3,"",MEDIAN(Ввод!B11,Ввод!B24,Ввод!B37))</f>
-        <v/>
-      </c>
-      <c r="D18" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="D18" s="3">
         <f>IF(COUNT(Ввод!B11,Ввод!B24,Ввод!B37)&lt;3,"",MAX(Ввод!B11,Ввод!B24,Ввод!B37))</f>
-        <v/>
-      </c>
-      <c r="E18" s="3" t="str">
+        <v>7</v>
+      </c>
+      <c r="E18" s="3">
         <f>IF(COUNT(Ввод!C11,Ввод!C24,Ввод!C37)&lt;3,"",MIN(Ввод!C11,Ввод!C24,Ввод!C37))</f>
-        <v/>
-      </c>
-      <c r="F18" s="3" t="str">
+        <v>8</v>
+      </c>
+      <c r="F18" s="3">
         <f>IF(COUNT(Ввод!C11,Ввод!C24,Ввод!C37)&lt;3,"",MEDIAN(Ввод!C11,Ввод!C24,Ввод!C37))</f>
-        <v/>
-      </c>
-      <c r="G18" s="3" t="str">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3">
         <f>IF(COUNT(Ввод!C11,Ввод!C24,Ввод!C37)&lt;3,"",MAX(Ввод!C11,Ввод!C24,Ввод!C37))</f>
-        <v/>
-      </c>
-      <c r="H18" s="3" t="str">
+        <v>8</v>
+      </c>
+      <c r="H18" s="3">
         <f>IF(COUNT(Ввод!D11,Ввод!D24,Ввод!D37)&lt;3,"",MIN(Ввод!D11,Ввод!D24,Ввод!D37))</f>
-        <v/>
-      </c>
-      <c r="I18" s="3" t="str">
+        <v>5</v>
+      </c>
+      <c r="I18" s="3">
         <f>IF(COUNT(Ввод!D11,Ввод!D24,Ввод!D37)&lt;3,"",MEDIAN(Ввод!D11,Ввод!D24,Ввод!D37))</f>
-        <v/>
-      </c>
-      <c r="J18" s="3" t="str">
+        <v>5</v>
+      </c>
+      <c r="J18" s="3">
         <f>IF(COUNT(Ввод!D11,Ввод!D24,Ввод!D37)&lt;3,"",MAX(Ввод!D11,Ввод!D24,Ввод!D37))</f>
-        <v/>
-      </c>
-      <c r="K18" s="3" t="str">
+        <v>6</v>
+      </c>
+      <c r="K18" s="3">
         <f>IF(COUNT(Ввод!E11,Ввод!E24,Ввод!E37)&lt;3,"",MIN(Ввод!E11,Ввод!E24,Ввод!E37))</f>
-        <v/>
-      </c>
-      <c r="L18" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="L18" s="3">
         <f>IF(COUNT(Ввод!E11,Ввод!E24,Ввод!E37)&lt;3,"",MEDIAN(Ввод!E11,Ввод!E24,Ввод!E37))</f>
-        <v/>
-      </c>
-      <c r="M18" s="3" t="str">
+        <v>5</v>
+      </c>
+      <c r="M18" s="3">
         <f>IF(COUNT(Ввод!E11,Ввод!E24,Ввод!E37)&lt;3,"",MAX(Ввод!E11,Ввод!E24,Ввод!E37))</f>
-        <v/>
-      </c>
-      <c r="N18" s="3" t="str">
+        <v>5</v>
+      </c>
+      <c r="N18" s="3">
         <f>IF(COUNT(Ввод!F11,Ввод!F24,Ввод!F37)&lt;3,"",MIN(Ввод!F11,Ввод!F24,Ввод!F37))</f>
-        <v/>
-      </c>
-      <c r="O18" s="3" t="str">
+        <v>5</v>
+      </c>
+      <c r="O18" s="3">
         <f>IF(COUNT(Ввод!F11,Ввод!F24,Ввод!F37)&lt;3,"",MEDIAN(Ввод!F11,Ввод!F24,Ввод!F37))</f>
-        <v/>
-      </c>
-      <c r="P18" s="3" t="str">
+        <v>5</v>
+      </c>
+      <c r="P18" s="3">
         <f>IF(COUNT(Ввод!F11,Ввод!F24,Ввод!F37)&lt;3,"",MAX(Ввод!F11,Ввод!F24,Ввод!F37))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>51</v>
       </c>
@@ -1847,7 +1911,7 @@
       <c r="O21" s="13"/>
       <c r="P21" s="14"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" s="4" t="s">
         <v>44</v>
@@ -1895,276 +1959,276 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="str">
         <f>Справочник!$B$10</f>
         <v>Бронь</v>
       </c>
-      <c r="B23" s="7" t="str">
+      <c r="B23" s="7">
         <f>IFERROR(IF(Справочник!$C$17="-",MIN($B$15:$B$18)/D15,B15/MAX($D$15:$D$18)),"")</f>
-        <v/>
-      </c>
-      <c r="C23" s="7" t="str">
+        <v>0.625</v>
+      </c>
+      <c r="C23" s="7">
         <f>IFERROR(IF(Справочник!$C$17="-",MIN($B$15:$B$18)/C15,C15/MAX($D$15:$D$18)),"")</f>
-        <v/>
-      </c>
-      <c r="D23" s="7" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="D23" s="7">
         <f>IFERROR(IF(Справочник!$C$17="-",MIN($B$15:$B$18)/B15,D15/MAX($D$15:$D$18)),"")</f>
-        <v/>
-      </c>
-      <c r="E23" s="7" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="E23" s="7">
         <f>IFERROR(IF(Справочник!$C$18="-",MIN($E$15:$E$18)/G15,E15/MAX($G$15:$G$18)),"")</f>
-        <v/>
-      </c>
-      <c r="F23" s="7" t="str">
+        <v>0.875</v>
+      </c>
+      <c r="F23" s="7">
         <f>IFERROR(IF(Справочник!$C$18="-",MIN($E$15:$E$18)/F15,F15/MAX($G$15:$G$18)),"")</f>
-        <v/>
-      </c>
-      <c r="G23" s="7" t="str">
+        <v>0.875</v>
+      </c>
+      <c r="G23" s="7">
         <f>IFERROR(IF(Справочник!$C$18="-",MIN($E$15:$E$18)/E15,G15/MAX($G$15:$G$18)),"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="7" t="str">
+        <v>1</v>
+      </c>
+      <c r="H23" s="7">
         <f>IFERROR(IF(Справочник!$C$19="-",MIN($H$15:$H$18)/J15,H15/MAX($J$15:$J$18)),"")</f>
-        <v/>
-      </c>
-      <c r="I23" s="7" t="str">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="I23" s="7">
         <f>IFERROR(IF(Справочник!$C$19="-",MIN($H$15:$H$18)/I15,I15/MAX($J$15:$J$18)),"")</f>
-        <v/>
-      </c>
-      <c r="J23" s="7" t="str">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="J23" s="7">
         <f>IFERROR(IF(Справочник!$C$19="-",MIN($H$15:$H$18)/H15,J15/MAX($J$15:$J$18)),"")</f>
-        <v/>
-      </c>
-      <c r="K23" s="7" t="str">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="K23" s="7">
         <f>IFERROR(IF(Справочник!$C$20="-",MIN($K$15:$K$18)/M15,K15/MAX($M$15:$M$18)),"")</f>
-        <v/>
-      </c>
-      <c r="L23" s="7" t="str">
+        <v>0.625</v>
+      </c>
+      <c r="L23" s="7">
         <f>IFERROR(IF(Справочник!$C$20="-",MIN($K$15:$K$18)/L15,L15/MAX($M$15:$M$18)),"")</f>
-        <v/>
-      </c>
-      <c r="M23" s="7" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="M23" s="7">
         <f>IFERROR(IF(Справочник!$C$20="-",MIN($K$15:$K$18)/K15,M15/MAX($M$15:$M$18)),"")</f>
-        <v/>
-      </c>
-      <c r="N23" s="7" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="N23" s="7">
         <f>IFERROR(IF(Справочник!$C$21="-",MIN($N$15:$N$18)/P15,N15/MAX($P$15:$P$18)),"")</f>
-        <v/>
-      </c>
-      <c r="O23" s="7" t="str">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="O23" s="7">
         <f>IFERROR(IF(Справочник!$C$21="-",MIN($N$15:$N$18)/O15,O15/MAX($P$15:$P$18)),"")</f>
-        <v/>
-      </c>
-      <c r="P23" s="7" t="str">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="P23" s="7">
         <f>IFERROR(IF(Справочник!$C$21="-",MIN($N$15:$N$18)/N15,P15/MAX($P$15:$P$18)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="str">
         <f>Справочник!$B$11</f>
         <v>Бюджет</v>
       </c>
-      <c r="B24" s="7" t="str">
+      <c r="B24" s="7">
         <f>IFERROR(IF(Справочник!$C$17="-",MIN($B$15:$B$18)/D16,B16/MAX($D$15:$D$18)),"")</f>
-        <v/>
-      </c>
-      <c r="C24" s="7" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="C24" s="7">
         <f>IFERROR(IF(Справочник!$C$17="-",MIN($B$15:$B$18)/C16,C16/MAX($D$15:$D$18)),"")</f>
-        <v/>
-      </c>
-      <c r="D24" s="7" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="D24" s="7">
         <f>IFERROR(IF(Справочник!$C$17="-",MIN($B$15:$B$18)/B16,D16/MAX($D$15:$D$18)),"")</f>
-        <v/>
-      </c>
-      <c r="E24" s="7" t="str">
+        <v>0.875</v>
+      </c>
+      <c r="E24" s="7">
         <f>IFERROR(IF(Справочник!$C$18="-",MIN($E$15:$E$18)/G16,E16/MAX($G$15:$G$18)),"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="7" t="str">
+        <v>0.625</v>
+      </c>
+      <c r="F24" s="7">
         <f>IFERROR(IF(Справочник!$C$18="-",MIN($E$15:$E$18)/F16,F16/MAX($G$15:$G$18)),"")</f>
-        <v/>
-      </c>
-      <c r="G24" s="7" t="str">
+        <v>0.625</v>
+      </c>
+      <c r="G24" s="7">
         <f>IFERROR(IF(Справочник!$C$18="-",MIN($E$15:$E$18)/E16,G16/MAX($G$15:$G$18)),"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="7" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="H24" s="7">
         <f>IFERROR(IF(Справочник!$C$19="-",MIN($H$15:$H$18)/J16,H16/MAX($J$15:$J$18)),"")</f>
-        <v/>
-      </c>
-      <c r="I24" s="7" t="str">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="I24" s="7">
         <f>IFERROR(IF(Справочник!$C$19="-",MIN($H$15:$H$18)/I16,I16/MAX($J$15:$J$18)),"")</f>
-        <v/>
-      </c>
-      <c r="J24" s="7" t="str">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J24" s="7">
         <f>IFERROR(IF(Справочник!$C$19="-",MIN($H$15:$H$18)/H16,J16/MAX($J$15:$J$18)),"")</f>
-        <v/>
-      </c>
-      <c r="K24" s="7" t="str">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="K24" s="7">
         <f>IFERROR(IF(Справочник!$C$20="-",MIN($K$15:$K$18)/M16,K16/MAX($M$15:$M$18)),"")</f>
-        <v/>
-      </c>
-      <c r="L24" s="7" t="str">
+        <v>0.625</v>
+      </c>
+      <c r="L24" s="7">
         <f>IFERROR(IF(Справочник!$C$20="-",MIN($K$15:$K$18)/L16,L16/MAX($M$15:$M$18)),"")</f>
-        <v/>
-      </c>
-      <c r="M24" s="7" t="str">
+        <v>0.625</v>
+      </c>
+      <c r="M24" s="7">
         <f>IFERROR(IF(Справочник!$C$20="-",MIN($K$15:$K$18)/K16,M16/MAX($M$15:$M$18)),"")</f>
-        <v/>
-      </c>
-      <c r="N24" s="7" t="str">
+        <v>0.625</v>
+      </c>
+      <c r="N24" s="7">
         <f>IFERROR(IF(Справочник!$C$21="-",MIN($N$15:$N$18)/P16,N16/MAX($P$15:$P$18)),"")</f>
-        <v/>
-      </c>
-      <c r="O24" s="7" t="str">
+        <v>1</v>
+      </c>
+      <c r="O24" s="7">
         <f>IFERROR(IF(Справочник!$C$21="-",MIN($N$15:$N$18)/O16,O16/MAX($P$15:$P$18)),"")</f>
-        <v/>
-      </c>
-      <c r="P24" s="7" t="str">
+        <v>1</v>
+      </c>
+      <c r="P24" s="7">
         <f>IFERROR(IF(Справочник!$C$21="-",MIN($N$15:$N$18)/N16,P16/MAX($P$15:$P$18)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="str">
         <f>Справочник!$B$12</f>
         <v>Запись</v>
       </c>
-      <c r="B25" s="7" t="str">
+      <c r="B25" s="7">
         <f>IFERROR(IF(Справочник!$C$17="-",MIN($B$15:$B$18)/D17,B17/MAX($D$15:$D$18)),"")</f>
-        <v/>
-      </c>
-      <c r="C25" s="7" t="str">
+        <v>1</v>
+      </c>
+      <c r="C25" s="7">
         <f>IFERROR(IF(Справочник!$C$17="-",MIN($B$15:$B$18)/C17,C17/MAX($D$15:$D$18)),"")</f>
-        <v/>
-      </c>
-      <c r="D25" s="7" t="str">
+        <v>1</v>
+      </c>
+      <c r="D25" s="7">
         <f>IFERROR(IF(Справочник!$C$17="-",MIN($B$15:$B$18)/B17,D17/MAX($D$15:$D$18)),"")</f>
-        <v/>
-      </c>
-      <c r="E25" s="7" t="str">
+        <v>1</v>
+      </c>
+      <c r="E25" s="7">
         <f>IFERROR(IF(Справочник!$C$18="-",MIN($E$15:$E$18)/G17,E17/MAX($G$15:$G$18)),"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="7" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="F25" s="7">
         <f>IFERROR(IF(Справочник!$C$18="-",MIN($E$15:$E$18)/F17,F17/MAX($G$15:$G$18)),"")</f>
-        <v/>
-      </c>
-      <c r="G25" s="7" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="G25" s="7">
         <f>IFERROR(IF(Справочник!$C$18="-",MIN($E$15:$E$18)/E17,G17/MAX($G$15:$G$18)),"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="7" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="H25" s="7">
         <f>IFERROR(IF(Справочник!$C$19="-",MIN($H$15:$H$18)/J17,H17/MAX($J$15:$J$18)),"")</f>
-        <v/>
-      </c>
-      <c r="I25" s="7" t="str">
+        <v>1</v>
+      </c>
+      <c r="I25" s="7">
         <f>IFERROR(IF(Справочник!$C$19="-",MIN($H$15:$H$18)/I17,I17/MAX($J$15:$J$18)),"")</f>
-        <v/>
-      </c>
-      <c r="J25" s="7" t="str">
+        <v>1</v>
+      </c>
+      <c r="J25" s="7">
         <f>IFERROR(IF(Справочник!$C$19="-",MIN($H$15:$H$18)/H17,J17/MAX($J$15:$J$18)),"")</f>
-        <v/>
-      </c>
-      <c r="K25" s="7" t="str">
+        <v>1</v>
+      </c>
+      <c r="K25" s="7">
         <f>IFERROR(IF(Справочник!$C$20="-",MIN($K$15:$K$18)/M17,K17/MAX($M$15:$M$18)),"")</f>
-        <v/>
-      </c>
-      <c r="L25" s="7" t="str">
+        <v>0.625</v>
+      </c>
+      <c r="L25" s="7">
         <f>IFERROR(IF(Справочник!$C$20="-",MIN($K$15:$K$18)/L17,L17/MAX($M$15:$M$18)),"")</f>
-        <v/>
-      </c>
-      <c r="M25" s="7" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="M25" s="7">
         <f>IFERROR(IF(Справочник!$C$20="-",MIN($K$15:$K$18)/K17,M17/MAX($M$15:$M$18)),"")</f>
-        <v/>
-      </c>
-      <c r="N25" s="7" t="str">
+        <v>1</v>
+      </c>
+      <c r="N25" s="7">
         <f>IFERROR(IF(Справочник!$C$21="-",MIN($N$15:$N$18)/P17,N17/MAX($P$15:$P$18)),"")</f>
-        <v/>
-      </c>
-      <c r="O25" s="7" t="str">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="O25" s="7">
         <f>IFERROR(IF(Справочник!$C$21="-",MIN($N$15:$N$18)/O17,O17/MAX($P$15:$P$18)),"")</f>
-        <v/>
-      </c>
-      <c r="P25" s="7" t="str">
+        <v>1</v>
+      </c>
+      <c r="P25" s="7">
         <f>IFERROR(IF(Справочник!$C$21="-",MIN($N$15:$N$18)/N17,P17/MAX($P$15:$P$18)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="str">
         <f>Справочник!$B$13</f>
         <v>Привычки</v>
       </c>
-      <c r="B26" s="7" t="str">
+      <c r="B26" s="7">
         <f>IFERROR(IF(Справочник!$C$17="-",MIN($B$15:$B$18)/D18,B18/MAX($D$15:$D$18)),"")</f>
-        <v/>
-      </c>
-      <c r="C26" s="7" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="C26" s="7">
         <f>IFERROR(IF(Справочник!$C$17="-",MIN($B$15:$B$18)/C18,C18/MAX($D$15:$D$18)),"")</f>
-        <v/>
-      </c>
-      <c r="D26" s="7" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="D26" s="7">
         <f>IFERROR(IF(Справочник!$C$17="-",MIN($B$15:$B$18)/B18,D18/MAX($D$15:$D$18)),"")</f>
-        <v/>
-      </c>
-      <c r="E26" s="7" t="str">
+        <v>0.875</v>
+      </c>
+      <c r="E26" s="7">
         <f>IFERROR(IF(Справочник!$C$18="-",MIN($E$15:$E$18)/G18,E18/MAX($G$15:$G$18)),"")</f>
-        <v/>
-      </c>
-      <c r="F26" s="7" t="str">
+        <v>1</v>
+      </c>
+      <c r="F26" s="7">
         <f>IFERROR(IF(Справочник!$C$18="-",MIN($E$15:$E$18)/F18,F18/MAX($G$15:$G$18)),"")</f>
-        <v/>
-      </c>
-      <c r="G26" s="7" t="str">
+        <v>1</v>
+      </c>
+      <c r="G26" s="7">
         <f>IFERROR(IF(Справочник!$C$18="-",MIN($E$15:$E$18)/E18,G18/MAX($G$15:$G$18)),"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="7" t="str">
+        <v>1</v>
+      </c>
+      <c r="H26" s="7">
         <f>IFERROR(IF(Справочник!$C$19="-",MIN($H$15:$H$18)/J18,H18/MAX($J$15:$J$18)),"")</f>
-        <v/>
-      </c>
-      <c r="I26" s="7" t="str">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="I26" s="7">
         <f>IFERROR(IF(Справочник!$C$19="-",MIN($H$15:$H$18)/I18,I18/MAX($J$15:$J$18)),"")</f>
-        <v/>
-      </c>
-      <c r="J26" s="7" t="str">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="J26" s="7">
         <f>IFERROR(IF(Справочник!$C$19="-",MIN($H$15:$H$18)/H18,J18/MAX($J$15:$J$18)),"")</f>
-        <v/>
-      </c>
-      <c r="K26" s="7" t="str">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="K26" s="7">
         <f>IFERROR(IF(Справочник!$C$20="-",MIN($K$15:$K$18)/M18,K18/MAX($M$15:$M$18)),"")</f>
-        <v/>
-      </c>
-      <c r="L26" s="7" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="L26" s="7">
         <f>IFERROR(IF(Справочник!$C$20="-",MIN($K$15:$K$18)/L18,L18/MAX($M$15:$M$18)),"")</f>
-        <v/>
-      </c>
-      <c r="M26" s="7" t="str">
+        <v>0.625</v>
+      </c>
+      <c r="M26" s="7">
         <f>IFERROR(IF(Справочник!$C$20="-",MIN($K$15:$K$18)/K18,M18/MAX($M$15:$M$18)),"")</f>
-        <v/>
-      </c>
-      <c r="N26" s="7" t="str">
+        <v>0.625</v>
+      </c>
+      <c r="N26" s="7">
         <f>IFERROR(IF(Справочник!$C$21="-",MIN($N$15:$N$18)/P18,N18/MAX($P$15:$P$18)),"")</f>
-        <v/>
-      </c>
-      <c r="O26" s="7" t="str">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="O26" s="7">
         <f>IFERROR(IF(Справочник!$C$21="-",MIN($N$15:$N$18)/O18,O18/MAX($P$15:$P$18)),"")</f>
-        <v/>
-      </c>
-      <c r="P26" s="7" t="str">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="P26" s="7">
         <f>IFERROR(IF(Справочник!$C$21="-",MIN($N$15:$N$18)/N18,P18/MAX($P$15:$P$18)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.7142857142857143</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>51</v>
       </c>
@@ -2199,7 +2263,7 @@
       <c r="O29" s="13"/>
       <c r="P29" s="14"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
         <v>44</v>
@@ -2247,276 +2311,276 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="str">
         <f>Справочник!$B$10</f>
         <v>Бронь</v>
       </c>
-      <c r="B31" s="8" t="str">
+      <c r="B31" s="8">
         <f>IFERROR(B23*$E$6,"")</f>
-        <v/>
-      </c>
-      <c r="C31" s="8" t="str">
+        <v>0.41666666666666663</v>
+      </c>
+      <c r="C31" s="8">
         <f>IFERROR(C23*$F$6,"")</f>
-        <v/>
-      </c>
-      <c r="D31" s="8" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="D31" s="8">
         <f>IFERROR(D23*$G$6,"")</f>
-        <v/>
-      </c>
-      <c r="E31" s="8" t="str">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E31" s="8">
         <f>IFERROR(E23*$E$7,"")</f>
-        <v/>
-      </c>
-      <c r="F31" s="8" t="str">
+        <v>0.58333333333333326</v>
+      </c>
+      <c r="F31" s="8">
         <f>IFERROR(F23*$F$7,"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="8" t="str">
+        <v>0.58333333333333326</v>
+      </c>
+      <c r="G31" s="8">
         <f>IFERROR(G23*$G$7,"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="8" t="str">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="H31" s="8">
         <f>IFERROR(H23*$E$8,"")</f>
-        <v/>
-      </c>
-      <c r="I31" s="8" t="str">
+        <v>0.69135802469135799</v>
+      </c>
+      <c r="I31" s="8">
         <f>IFERROR(I23*$F$8,"")</f>
-        <v/>
-      </c>
-      <c r="J31" s="8" t="str">
+        <v>0.79012345679012341</v>
+      </c>
+      <c r="J31" s="8">
         <f>IFERROR(J23*$G$8,"")</f>
-        <v/>
-      </c>
-      <c r="K31" s="8" t="str">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="K31" s="8">
         <f>IFERROR(K23*$E$9,"")</f>
-        <v/>
-      </c>
-      <c r="L31" s="8" t="str">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="L31" s="8">
         <f>IFERROR(L23*$F$9,"")</f>
-        <v/>
-      </c>
-      <c r="M31" s="8" t="str">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M31" s="8">
         <f>IFERROR(M23*$G$9,"")</f>
-        <v/>
-      </c>
-      <c r="N31" s="8" t="str">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="N31" s="8">
         <f>IFERROR(N23*$E$10,"")</f>
-        <v/>
-      </c>
-      <c r="O31" s="8" t="str">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="O31" s="8">
         <f>IFERROR(O23*$F$10,"")</f>
-        <v/>
-      </c>
-      <c r="P31" s="8" t="str">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="P31" s="8">
         <f>IFERROR(P23*$G$10,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="str">
         <f>Справочник!$B$11</f>
         <v>Бюджет</v>
       </c>
-      <c r="B32" s="8" t="str">
+      <c r="B32" s="8">
         <f>IFERROR(B24*$E$6,"")</f>
-        <v/>
-      </c>
-      <c r="C32" s="8" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="C32" s="8">
         <f>IFERROR(C24*$F$6,"")</f>
-        <v/>
-      </c>
-      <c r="D32" s="8" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="D32" s="8">
         <f>IFERROR(D24*$G$6,"")</f>
-        <v/>
-      </c>
-      <c r="E32" s="8" t="str">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="E32" s="8">
         <f>IFERROR(E24*$E$7,"")</f>
-        <v/>
-      </c>
-      <c r="F32" s="8" t="str">
+        <v>0.41666666666666663</v>
+      </c>
+      <c r="F32" s="8">
         <f>IFERROR(F24*$F$7,"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="8" t="str">
+        <v>0.41666666666666663</v>
+      </c>
+      <c r="G32" s="8">
         <f>IFERROR(G24*$G$7,"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="8" t="str">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H32" s="8">
         <f>IFERROR(H24*$E$8,"")</f>
-        <v/>
-      </c>
-      <c r="I32" s="8" t="str">
+        <v>0.4320987654320988</v>
+      </c>
+      <c r="I32" s="8">
         <f>IFERROR(I24*$F$8,"")</f>
-        <v/>
-      </c>
-      <c r="J32" s="8" t="str">
+        <v>0.59259259259259256</v>
+      </c>
+      <c r="J32" s="8">
         <f>IFERROR(J24*$G$8,"")</f>
-        <v/>
-      </c>
-      <c r="K32" s="8" t="str">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="K32" s="8">
         <f>IFERROR(K24*$E$9,"")</f>
-        <v/>
-      </c>
-      <c r="L32" s="8" t="str">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="L32" s="8">
         <f>IFERROR(L24*$F$9,"")</f>
-        <v/>
-      </c>
-      <c r="M32" s="8" t="str">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="M32" s="8">
         <f>IFERROR(M24*$G$9,"")</f>
-        <v/>
-      </c>
-      <c r="N32" s="8" t="str">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="N32" s="8">
         <f>IFERROR(N24*$E$10,"")</f>
-        <v/>
-      </c>
-      <c r="O32" s="8" t="str">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="O32" s="8">
         <f>IFERROR(O24*$F$10,"")</f>
-        <v/>
-      </c>
-      <c r="P32" s="8" t="str">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="P32" s="8">
         <f>IFERROR(P24*$G$10,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.77777777777777779</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="str">
         <f>Справочник!$B$12</f>
         <v>Запись</v>
       </c>
-      <c r="B33" s="8" t="str">
+      <c r="B33" s="8">
         <f>IFERROR(B25*$E$6,"")</f>
-        <v/>
-      </c>
-      <c r="C33" s="8" t="str">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C33" s="8">
         <f>IFERROR(C25*$F$6,"")</f>
-        <v/>
-      </c>
-      <c r="D33" s="8" t="str">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D33" s="8">
         <f>IFERROR(D25*$G$6,"")</f>
-        <v/>
-      </c>
-      <c r="E33" s="8" t="str">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="E33" s="8">
         <f>IFERROR(E25*$E$7,"")</f>
-        <v/>
-      </c>
-      <c r="F33" s="8" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="F33" s="8">
         <f>IFERROR(F25*$F$7,"")</f>
-        <v/>
-      </c>
-      <c r="G33" s="8" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="G33" s="8">
         <f>IFERROR(G25*$G$7,"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="8" t="str">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H33" s="8">
         <f>IFERROR(H25*$E$8,"")</f>
-        <v/>
-      </c>
-      <c r="I33" s="8" t="str">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="I33" s="8">
         <f>IFERROR(I25*$F$8,"")</f>
-        <v/>
-      </c>
-      <c r="J33" s="8" t="str">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="J33" s="8">
         <f>IFERROR(J25*$G$8,"")</f>
-        <v/>
-      </c>
-      <c r="K33" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="K33" s="8">
         <f>IFERROR(K25*$E$9,"")</f>
-        <v/>
-      </c>
-      <c r="L33" s="8" t="str">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="L33" s="8">
         <f>IFERROR(L25*$F$9,"")</f>
-        <v/>
-      </c>
-      <c r="M33" s="8" t="str">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M33" s="8">
         <f>IFERROR(M25*$G$9,"")</f>
-        <v/>
-      </c>
-      <c r="N33" s="8" t="str">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="N33" s="8">
         <f>IFERROR(N25*$E$10,"")</f>
-        <v/>
-      </c>
-      <c r="O33" s="8" t="str">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="O33" s="8">
         <f>IFERROR(O25*$F$10,"")</f>
-        <v/>
-      </c>
-      <c r="P33" s="8" t="str">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="P33" s="8">
         <f>IFERROR(P25*$G$10,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.77777777777777779</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="str">
         <f>Справочник!$B$13</f>
         <v>Привычки</v>
       </c>
-      <c r="B34" s="8" t="str">
+      <c r="B34" s="8">
         <f>IFERROR(B26*$E$6,"")</f>
-        <v/>
-      </c>
-      <c r="C34" s="8" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="C34" s="8">
         <f>IFERROR(C26*$F$6,"")</f>
-        <v/>
-      </c>
-      <c r="D34" s="8" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="D34" s="8">
         <f>IFERROR(D26*$G$6,"")</f>
-        <v/>
-      </c>
-      <c r="E34" s="8" t="str">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="E34" s="8">
         <f>IFERROR(E26*$E$7,"")</f>
-        <v/>
-      </c>
-      <c r="F34" s="8" t="str">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F34" s="8">
         <f>IFERROR(F26*$F$7,"")</f>
-        <v/>
-      </c>
-      <c r="G34" s="8" t="str">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G34" s="8">
         <f>IFERROR(G26*$G$7,"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="8" t="str">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="H34" s="8">
         <f>IFERROR(H26*$E$8,"")</f>
-        <v/>
-      </c>
-      <c r="I34" s="8" t="str">
+        <v>0.4320987654320988</v>
+      </c>
+      <c r="I34" s="8">
         <f>IFERROR(I26*$F$8,"")</f>
-        <v/>
-      </c>
-      <c r="J34" s="8" t="str">
+        <v>0.49382716049382713</v>
+      </c>
+      <c r="J34" s="8">
         <f>IFERROR(J26*$G$8,"")</f>
-        <v/>
-      </c>
-      <c r="K34" s="8" t="str">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="K34" s="8">
         <f>IFERROR(K26*$E$9,"")</f>
-        <v/>
-      </c>
-      <c r="L34" s="8" t="str">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="L34" s="8">
         <f>IFERROR(L26*$F$9,"")</f>
-        <v/>
-      </c>
-      <c r="M34" s="8" t="str">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="M34" s="8">
         <f>IFERROR(M26*$G$9,"")</f>
-        <v/>
-      </c>
-      <c r="N34" s="8" t="str">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="N34" s="8">
         <f>IFERROR(N26*$E$10,"")</f>
-        <v/>
-      </c>
-      <c r="O34" s="8" t="str">
+        <v>0.47619047619047616</v>
+      </c>
+      <c r="O34" s="8">
         <f>IFERROR(O26*$F$10,"")</f>
-        <v/>
-      </c>
-      <c r="P34" s="8" t="str">
+        <v>0.47619047619047616</v>
+      </c>
+      <c r="P34" s="8">
         <f>IFERROR(P26*$G$10,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.55555555555555558</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>24</v>
       </c>
@@ -2541,62 +2605,62 @@
         <v>Интерес и экспертиза команды</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B38" s="8" t="str">
+      <c r="B38" s="8">
         <f>IF(COUNT(D31:D34)&lt;4,"",MAX(D31:D34))</f>
-        <v/>
-      </c>
-      <c r="C38" s="8" t="str">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="C38" s="8">
         <f>IF(COUNT(G31:G34)&lt;4,"",MAX(G31:G34))</f>
-        <v/>
-      </c>
-      <c r="D38" s="8" t="str">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="D38" s="8">
         <f>IF(COUNT(J31:J34)&lt;4,"",MAX(J31:J34))</f>
-        <v/>
-      </c>
-      <c r="E38" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="E38" s="8">
         <f>IF(COUNT(M31:M34)&lt;4,"",MAX(M31:M34))</f>
-        <v/>
-      </c>
-      <c r="F38" s="8" t="str">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="F38" s="8">
         <f>IF(COUNT(P31:P34)&lt;4,"",MAX(P31:P34))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.77777777777777779</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B39" s="8" t="str">
+      <c r="B39" s="8">
         <f>IF(COUNT(B31:B34)&lt;4,"",MIN(B31:B34))</f>
-        <v/>
-      </c>
-      <c r="C39" s="8" t="str">
+        <v>0.41666666666666663</v>
+      </c>
+      <c r="C39" s="8">
         <f>IF(COUNT(E31:E34)&lt;4,"",MIN(E31:E34))</f>
-        <v/>
-      </c>
-      <c r="D39" s="8" t="str">
+        <v>0.41666666666666663</v>
+      </c>
+      <c r="D39" s="8">
         <f>IF(COUNT(H31:H34)&lt;4,"",MIN(H31:H34))</f>
-        <v/>
-      </c>
-      <c r="E39" s="8" t="str">
+        <v>0.4320987654320988</v>
+      </c>
+      <c r="E39" s="8">
         <f>IF(COUNT(K31:K34)&lt;4,"",MIN(K31:K34))</f>
-        <v/>
-      </c>
-      <c r="F39" s="8" t="str">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="F39" s="8">
         <f>IF(COUNT(N31:N34)&lt;4,"",MIN(N31:N34))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.47619047619047616</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>51</v>
       </c>
@@ -2613,101 +2677,96 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="str">
         <f>Справочник!$B$10</f>
         <v>Бронь</v>
       </c>
-      <c r="B43" s="8" t="str">
+      <c r="B43" s="8">
         <f>IFERROR(SQRT(((B31-$B$38)^2+(C31-$B$38)^2+(D31-$B$38)^2)/3)+SQRT(((E31-$C$38)^2+(F31-$C$38)^2+(G31-$C$38)^2)/3)+SQRT(((H31-$D$38)^2+(I31-$D$38)^2+(J31-$D$38)^2)/3)+SQRT(((K31-$E$38)^2+(L31-$E$38)^2+(M31-$E$38)^2)/3)+SQRT(((N31-$F$38)^2+(O31-$F$38)^2+(P31-$F$38)^2)/3),"")</f>
-        <v/>
-      </c>
-      <c r="C43" s="8" t="str">
+        <v>1.0462903278762354</v>
+      </c>
+      <c r="C43" s="8">
         <f>IFERROR(SQRT(((B31-$B$39)^2+(C31-$B$39)^2+(D31-$B$39)^2)/3)+SQRT(((E31-$C$39)^2+(F31-$C$39)^2+(G31-$C$39)^2)/3)+SQRT(((H31-$D$39)^2+(I31-$D$39)^2+(J31-$D$39)^2)/3)+SQRT(((K31-$E$39)^2+(L31-$E$39)^2+(M31-$E$39)^2)/3)+SQRT(((N31-$F$39)^2+(O31-$F$39)^2+(P31-$F$39)^2)/3),"")</f>
-        <v/>
-      </c>
-      <c r="D43" s="10" t="str">
+        <v>1.0202040447240044</v>
+      </c>
+      <c r="D43" s="10">
         <f>IFERROR(C43/(B43+C43),"")</f>
-        <v/>
-      </c>
-      <c r="E43" s="11" t="str">
+        <v>0.49368827626677558</v>
+      </c>
+      <c r="E43" s="11">
         <f>IFERROR(RANK(D43,$D$43:$D$46,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="str">
         <f>Справочник!$B$11</f>
         <v>Бюджет</v>
       </c>
-      <c r="B44" s="8" t="str">
+      <c r="B44" s="8">
         <f>IFERROR(SQRT(((B32-$B$38)^2+(C32-$B$38)^2+(D32-$B$38)^2)/3)+SQRT(((E32-$C$38)^2+(F32-$C$38)^2+(G32-$C$38)^2)/3)+SQRT(((H32-$D$38)^2+(I32-$D$38)^2+(J32-$D$38)^2)/3)+SQRT(((K32-$E$38)^2+(L32-$E$38)^2+(M32-$E$38)^2)/3)+SQRT(((N32-$F$38)^2+(O32-$F$38)^2+(P32-$F$38)^2)/3),"")</f>
-        <v/>
-      </c>
-      <c r="C44" s="8" t="str">
+        <v>1.2970774570199077</v>
+      </c>
+      <c r="C44" s="8">
         <f>IFERROR(SQRT(((B32-$B$39)^2+(C32-$B$39)^2+(D32-$B$39)^2)/3)+SQRT(((E32-$C$39)^2+(F32-$C$39)^2+(G32-$C$39)^2)/3)+SQRT(((H32-$D$39)^2+(I32-$D$39)^2+(J32-$D$39)^2)/3)+SQRT(((K32-$E$39)^2+(L32-$E$39)^2+(M32-$E$39)^2)/3)+SQRT(((N32-$F$39)^2+(O32-$F$39)^2+(P32-$F$39)^2)/3),"")</f>
-        <v/>
-      </c>
-      <c r="D44" s="10" t="str">
+        <v>0.82357226988759191</v>
+      </c>
+      <c r="D44" s="10">
         <f>IFERROR(C44/(B44+C44),"")</f>
-        <v/>
-      </c>
-      <c r="E44" s="11" t="str">
+        <v>0.38835846365283083</v>
+      </c>
+      <c r="E44" s="11">
         <f>IFERROR(RANK(D44,$D$43:$D$46,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="str">
         <f>Справочник!$B$12</f>
         <v>Запись</v>
       </c>
-      <c r="B45" s="8" t="str">
+      <c r="B45" s="8">
         <f>IFERROR(SQRT(((B33-$B$38)^2+(C33-$B$38)^2+(D33-$B$38)^2)/3)+SQRT(((E33-$C$38)^2+(F33-$C$38)^2+(G33-$C$38)^2)/3)+SQRT(((H33-$D$38)^2+(I33-$D$38)^2+(J33-$D$38)^2)/3)+SQRT(((K33-$E$38)^2+(L33-$E$38)^2+(M33-$E$38)^2)/3)+SQRT(((N33-$F$38)^2+(O33-$F$38)^2+(P33-$F$38)^2)/3),"")</f>
-        <v/>
-      </c>
-      <c r="C45" s="8" t="str">
+        <v>0.80184717406267458</v>
+      </c>
+      <c r="C45" s="8">
         <f>IFERROR(SQRT(((B33-$B$39)^2+(C33-$B$39)^2+(D33-$B$39)^2)/3)+SQRT(((E33-$C$39)^2+(F33-$C$39)^2+(G33-$C$39)^2)/3)+SQRT(((H33-$D$39)^2+(I33-$D$39)^2+(J33-$D$39)^2)/3)+SQRT(((K33-$E$39)^2+(L33-$E$39)^2+(M33-$E$39)^2)/3)+SQRT(((N33-$F$39)^2+(O33-$F$39)^2+(P33-$F$39)^2)/3),"")</f>
-        <v/>
-      </c>
-      <c r="D45" s="10" t="str">
+        <v>1.3135931001468368</v>
+      </c>
+      <c r="D45" s="10">
         <f>IFERROR(C45/(B45+C45),"")</f>
-        <v/>
-      </c>
-      <c r="E45" s="11" t="str">
+        <v>0.62095494548419461</v>
+      </c>
+      <c r="E45" s="11">
         <f>IFERROR(RANK(D45,$D$43:$D$46,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="str">
         <f>Справочник!$B$13</f>
         <v>Привычки</v>
       </c>
-      <c r="B46" s="8" t="str">
+      <c r="B46" s="8">
         <f>IFERROR(SQRT(((B34-$B$38)^2+(C34-$B$38)^2+(D34-$B$38)^2)/3)+SQRT(((E34-$C$38)^2+(F34-$C$38)^2+(G34-$C$38)^2)/3)+SQRT(((H34-$D$38)^2+(I34-$D$38)^2+(J34-$D$38)^2)/3)+SQRT(((K34-$E$38)^2+(L34-$E$38)^2+(M34-$E$38)^2)/3)+SQRT(((N34-$F$38)^2+(O34-$F$38)^2+(P34-$F$38)^2)/3),"")</f>
-        <v/>
-      </c>
-      <c r="C46" s="8" t="str">
+        <v>1.3384094908739552</v>
+      </c>
+      <c r="C46" s="8">
         <f>IFERROR(SQRT(((B34-$B$39)^2+(C34-$B$39)^2+(D34-$B$39)^2)/3)+SQRT(((E34-$C$39)^2+(F34-$C$39)^2+(G34-$C$39)^2)/3)+SQRT(((H34-$D$39)^2+(I34-$D$39)^2+(J34-$D$39)^2)/3)+SQRT(((K34-$E$39)^2+(L34-$E$39)^2+(M34-$E$39)^2)/3)+SQRT(((N34-$F$39)^2+(O34-$F$39)^2+(P34-$F$39)^2)/3),"")</f>
-        <v/>
-      </c>
-      <c r="D46" s="10" t="str">
+        <v>0.74655853330725375</v>
+      </c>
+      <c r="D46" s="10">
         <f>IFERROR(C46/(B46+C46),"")</f>
-        <v/>
-      </c>
-      <c r="E46" s="11" t="str">
+        <v>0.35806713803221796</v>
+      </c>
+      <c r="E46" s="11">
         <f>IFERROR(RANK(D46,$D$43:$D$46,0),"")</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:G29"/>
     <mergeCell ref="N29:P29"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="K13:M13"/>
@@ -2718,6 +2777,11 @@
     <mergeCell ref="H29:J29"/>
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="N21:P21"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:G29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
